--- a/exports/ASTRAL_full_report.xlsx
+++ b/exports/ASTRAL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.56</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1786.45</v>
+        <v>1705.25</v>
       </c>
       <c r="I2" t="n">
         <v>1757.81347953553</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.52</v>
+        <v>-7.9</v>
       </c>
       <c r="L2" t="n">
-        <v>4.29</v>
+        <v>11.88</v>
       </c>
       <c r="M2" t="n">
         <v>0.48</v>
       </c>
       <c r="N2" t="n">
-        <v>2.92</v>
+        <v>9.43</v>
       </c>
       <c r="O2" t="n">
         <v>0.6</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44631.38541666666</v>
+        <v>44631.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>1461.75</v>
+        <v>1469.15</v>
       </c>
       <c r="I3" t="n">
         <v>1464.958255256594</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>14.28</v>
+        <v>13.85</v>
       </c>
       <c r="L3" t="n">
         <v>4.85</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>7.38</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1543.25</v>
+        <v>1513.35</v>
       </c>
       <c r="I4" t="n">
         <v>1525.82417424819</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>53.83333333333334</v>
+        <v>54</v>
       </c>
       <c r="K4" t="n">
-        <v>5.04</v>
+        <v>3.01</v>
       </c>
       <c r="L4" t="n">
         <v>2.1</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.24</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44712.55208333334</v>
+        <v>44713.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1300.75</v>
+        <v>1361.3</v>
       </c>
       <c r="I5" t="n">
         <v>1329.676413629178</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>14.05</v>
+        <v>10.05</v>
       </c>
       <c r="L5" t="n">
         <v>2.5</v>
@@ -726,7 +785,7 @@
         <v>1.97</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>4.91</v>
       </c>
       <c r="O5" t="n">
         <v>-2.76</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.02</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1281.55</v>
+        <v>1255.8</v>
       </c>
       <c r="I6" t="n">
         <v>1256.992168473643</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.86</v>
+        <v>-7.75</v>
       </c>
       <c r="L6" t="n">
-        <v>5.96</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M6" t="n">
         <v>0.91</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
         <v>4.91</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.58</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44746.38541666666</v>
+        <v>44746.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>1270.75</v>
+        <v>1298.5</v>
       </c>
       <c r="I7" t="n">
         <v>1296.358574920318</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.19</v>
+        <v>-3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="M7" t="n">
         <v>1.99</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.5</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44820.38541666666</v>
+        <v>44820.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>1799.65</v>
+        <v>1765.2</v>
       </c>
       <c r="I8" t="n">
         <v>1782.992785528925</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>73.83333333333333</v>
+        <v>74</v>
       </c>
       <c r="K8" t="n">
-        <v>38.59</v>
+        <v>35.94</v>
       </c>
       <c r="L8" t="n">
         <v>3.38</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44866.38541666666</v>
+        <v>44866.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>1538.4</v>
+        <v>1552.6</v>
       </c>
       <c r="I9" t="n">
         <v>1551.689703193073</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45.83333333333334</v>
+        <v>46</v>
       </c>
       <c r="K9" t="n">
-        <v>12.85</v>
+        <v>12.04</v>
       </c>
       <c r="L9" t="n">
         <v>5.78</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>5.74</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44876.55208333334</v>
+        <v>44879.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1548.85</v>
+        <v>1489.55</v>
       </c>
       <c r="I10" t="n">
         <v>1506.384489338841</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.24</v>
+        <v>-4.06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.96</v>
+        <v>8.83</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6</v>
+        <v>3.17</v>
       </c>
       <c r="N10" t="n">
-        <v>1.18</v>
+        <v>3.62</v>
       </c>
       <c r="O10" t="n">
         <v>1.37</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.17</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44896.55208333334</v>
+        <v>44897.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1449.6</v>
+        <v>1497.2</v>
       </c>
       <c r="I11" t="n">
         <v>1467.637000152226</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>2.68</v>
+        <v>-0.51</v>
       </c>
       <c r="L11" t="n">
         <v>2.47</v>
@@ -1068,7 +1199,7 @@
         <v>0.86</v>
       </c>
       <c r="N11" t="n">
-        <v>2.33</v>
+        <v>4.66</v>
       </c>
       <c r="O11" t="n">
         <v>-3.62</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.66</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44914.55208333334</v>
+        <v>44915.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1530.1</v>
+        <v>1512.15</v>
       </c>
       <c r="I12" t="n">
         <v>1514.317419062168</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>3.08</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>5.95</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44931.55208333334</v>
+        <v>44932.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1513.5</v>
+        <v>1552.95</v>
       </c>
       <c r="I13" t="n">
         <v>1518.80218929841</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.09</v>
+        <v>-2.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>3.92</v>
       </c>
       <c r="M13" t="n">
         <v>0.95</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.99</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44942.38541666666</v>
+        <v>44942.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1512.2</v>
+        <v>1482.7</v>
       </c>
       <c r="I14" t="n">
         <v>1488.340502411461</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.62</v>
+        <v>-4.52</v>
       </c>
       <c r="L14" t="n">
-        <v>3.35</v>
+        <v>5.59</v>
       </c>
       <c r="M14" t="n">
         <v>0.59</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>6.36</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44960.55208333334</v>
+        <v>44963.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1541.35</v>
+        <v>1563.9</v>
       </c>
       <c r="I15" t="n">
         <v>1546.833958377003</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.96</v>
+        <v>-5.48</v>
       </c>
       <c r="L15" t="n">
-        <v>5.78</v>
+        <v>7.15</v>
       </c>
       <c r="M15" t="n">
         <v>5.04</v>
       </c>
       <c r="N15" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O15" t="n">
         <v>-3.64</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>7.14</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44966.55208333334</v>
+        <v>44967.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1526.3</v>
+        <v>1458.7</v>
       </c>
       <c r="I16" t="n">
         <v>1466.300613023116</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.4</v>
+        <v>-6.73</v>
       </c>
       <c r="L16" t="n">
-        <v>4.66</v>
+        <v>7.55</v>
       </c>
       <c r="M16" t="n">
         <v>0.29</v>
       </c>
       <c r="N16" t="n">
-        <v>1.33</v>
+        <v>4.63</v>
       </c>
       <c r="O16" t="n">
         <v>2.01</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.09</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45021.55208333334</v>
+        <v>45022.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1332</v>
+        <v>1391.55</v>
       </c>
       <c r="I17" t="n">
         <v>1371.624080291725</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K17" t="n">
-        <v>8.69</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>5.15</v>
@@ -1410,7 +1613,7 @@
         <v>1.44</v>
       </c>
       <c r="N17" t="n">
-        <v>2.66</v>
+        <v>4.87</v>
       </c>
       <c r="O17" t="n">
         <v>-4.63</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.13</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45041.38541666666</v>
+        <v>45041.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>1399</v>
+        <v>1390.1</v>
       </c>
       <c r="I18" t="n">
         <v>1393.334835573622</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>0.54</v>
+        <v>-0.1</v>
       </c>
       <c r="L18" t="n">
         <v>3.88</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>4.54</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45044.38541666666</v>
+        <v>45044.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>1435.15</v>
+        <v>1449</v>
       </c>
       <c r="I19" t="n">
         <v>1442.328073864959</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.24</v>
+        <v>-4.24</v>
       </c>
       <c r="L19" t="n">
-        <v>3.73</v>
+        <v>4.38</v>
       </c>
       <c r="M19" t="n">
         <v>0.73</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.39</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45111.55208333334</v>
+        <v>45112.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1922.2</v>
+        <v>1887.9</v>
       </c>
       <c r="I20" t="n">
         <v>1917.567052117259</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>67</v>
+        <v>67.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>32.66</v>
+        <v>30.29</v>
       </c>
       <c r="L20" t="n">
         <v>0.98</v>
@@ -1581,7 +1820,7 @@
         <v>0.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.19</v>
+        <v>2.72</v>
       </c>
       <c r="O20" t="n">
         <v>3.72</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.29</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45125.55208333334</v>
+        <v>45126.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1840</v>
+        <v>1891.7</v>
       </c>
       <c r="I21" t="n">
         <v>1873.725842791824</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>2.54</v>
+        <v>-0.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.86</v>
@@ -1638,7 +1889,7 @@
         <v>1.35</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
         <v>-2.72</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.68</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45169.55208333334</v>
+        <v>45170.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1951</v>
+        <v>1919</v>
       </c>
       <c r="I22" t="n">
         <v>1922.117036197456</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K22" t="n">
-        <v>3.13</v>
+        <v>1.44</v>
       </c>
       <c r="L22" t="n">
         <v>2.73</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.39</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45194.55208333334</v>
+        <v>45195.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1867</v>
+        <v>1911.05</v>
       </c>
       <c r="I23" t="n">
         <v>1909.266361801651</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>2.71</v>
+        <v>0.41</v>
       </c>
       <c r="L23" t="n">
         <v>1.96</v>
@@ -1752,7 +2027,7 @@
         <v>0.79</v>
       </c>
       <c r="N23" t="n">
-        <v>1.22</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>-2</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>6.14</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45217.55208333334</v>
+        <v>45218.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1950.9</v>
+        <v>1849.5</v>
       </c>
       <c r="I24" t="n">
         <v>1893.142675714972</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K24" t="n">
-        <v>2.09</v>
+        <v>-3.22</v>
       </c>
       <c r="L24" t="n">
-        <v>3.11</v>
+        <v>3.61</v>
       </c>
       <c r="M24" t="n">
         <v>0.74</v>
       </c>
       <c r="N24" t="n">
-        <v>1.9</v>
+        <v>5.33</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.96</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45237.55208333334</v>
+        <v>45238.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1872.85</v>
+        <v>1892.2</v>
       </c>
       <c r="I25" t="n">
         <v>1883.318025574622</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.26</v>
+        <v>-2.31</v>
       </c>
       <c r="L25" t="n">
         <v>5.7</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>4.37</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1935.75</v>
+        <v>1869.7</v>
       </c>
       <c r="I26" t="n">
         <v>1905.145739877579</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>-1.19</v>
       </c>
       <c r="L26" t="n">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="M26" t="n">
         <v>0.42</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.82</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45310.38541666666</v>
+        <v>45310.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1831.9</v>
+        <v>1855</v>
       </c>
       <c r="I27" t="n">
         <v>1845.877038373791</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>2.02</v>
+        <v>0.79</v>
       </c>
       <c r="L27" t="n">
         <v>4.08</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>5.05</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>2009.15</v>
+        <v>1981</v>
       </c>
       <c r="I28" t="n">
         <v>1985.020020247688</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>53.83333333333334</v>
+        <v>54</v>
       </c>
       <c r="K28" t="n">
-        <v>8.31</v>
+        <v>6.79</v>
       </c>
       <c r="L28" t="n">
         <v>4.85</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.45</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45408.55208333334</v>
+        <v>45411.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>2043</v>
+        <v>2056.75</v>
       </c>
       <c r="I29" t="n">
         <v>2044.190846293683</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>44</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.13</v>
+        <v>-3.82</v>
       </c>
       <c r="L29" t="n">
         <v>6.01</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.2</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45430.38541666666</v>
+        <v>45433.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>2189.8</v>
+        <v>2077.1</v>
       </c>
       <c r="I30" t="n">
         <v>2170.491713343406</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>6.47</v>
+        <v>0.99</v>
       </c>
       <c r="L30" t="n">
         <v>1.64</v>
@@ -2151,7 +2510,7 @@
         <v>1.51</v>
       </c>
       <c r="N30" t="n">
-        <v>4.95</v>
+        <v>5.06</v>
       </c>
       <c r="O30" t="n">
         <v>0.34</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>12.11</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45453.55208333334</v>
+        <v>45454.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>2150</v>
+        <v>2214</v>
       </c>
       <c r="I31" t="n">
         <v>2200.162646578111</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.51</v>
+        <v>-6.59</v>
       </c>
       <c r="L31" t="n">
-        <v>6.15</v>
+        <v>7.34</v>
       </c>
       <c r="M31" t="n">
         <v>2.19</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.43</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45485.55208333334</v>
+        <v>45488.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>2291.85</v>
+        <v>2253.1</v>
       </c>
       <c r="I32" t="n">
         <v>2282.213796865107</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>3.52</v>
+        <v>1.77</v>
       </c>
       <c r="L32" t="n">
         <v>2.89</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.48</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45555.55208333334</v>
+        <v>45558.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1930</v>
+        <v>1966.7</v>
       </c>
       <c r="I33" t="n">
         <v>1955.767119081223</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K33" t="n">
-        <v>14.34</v>
+        <v>12.71</v>
       </c>
       <c r="L33" t="n">
         <v>2.79</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>4.57</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1973</v>
+        <v>1930.25</v>
       </c>
       <c r="I34" t="n">
         <v>1945.304963620636</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>0.32</v>
+        <v>-1.85</v>
       </c>
       <c r="L34" t="n">
-        <v>1.39</v>
+        <v>1.93</v>
       </c>
       <c r="M34" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="N34" t="n">
-        <v>1.09</v>
+        <v>2.59</v>
       </c>
       <c r="O34" t="n">
         <v>2.28</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>5.26</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1789.55</v>
+        <v>1813</v>
       </c>
       <c r="I35" t="n">
         <v>1795.746104707686</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K35" t="n">
-        <v>7.29</v>
+        <v>6.07</v>
       </c>
       <c r="L35" t="n">
         <v>2.16</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>5.29</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1807</v>
+        <v>1786.95</v>
       </c>
       <c r="I36" t="n">
         <v>1796.759584766834</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.33</v>
+        <v>-1.44</v>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>2.71</v>
       </c>
       <c r="M36" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="N36" t="n">
         <v>1.63</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>3.89</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45737.55208333334</v>
+        <v>45740.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1299.9</v>
+        <v>1327.5</v>
       </c>
       <c r="I37" t="n">
         <v>1311.993573334257</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>92.16666666666667</v>
+        <v>95</v>
       </c>
       <c r="K37" t="n">
-        <v>27.26</v>
+        <v>25.71</v>
       </c>
       <c r="L37" t="n">
         <v>0.68</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>5.75</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1338.6</v>
+        <v>1281.3</v>
       </c>
       <c r="I38" t="n">
         <v>1284.789616954073</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>0.84</v>
+        <v>-3.48</v>
       </c>
       <c r="L38" t="n">
-        <v>4.49</v>
+        <v>6.29</v>
       </c>
       <c r="M38" t="n">
-        <v>0.59</v>
+        <v>6.62</v>
       </c>
       <c r="N38" t="n">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
         <v>0.85</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>6.52</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1303.5</v>
+        <v>1337.7</v>
       </c>
       <c r="I39" t="n">
         <v>1335.040339339737</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.73</v>
+        <v>-4.4</v>
       </c>
       <c r="L39" t="n">
-        <v>3.54</v>
+        <v>4.61</v>
       </c>
       <c r="M39" t="n">
         <v>1.61</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.71</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45779.38541666666</v>
+        <v>45779.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>1320.1</v>
+        <v>1313.1</v>
       </c>
       <c r="I40" t="n">
         <v>1316.08445271803</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.32</v>
+        <v>-1.84</v>
       </c>
       <c r="L40" t="n">
         <v>2.37</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>6.93</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45792.55208333334</v>
+        <v>45793.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1346</v>
+        <v>1366.9</v>
       </c>
       <c r="I41" t="n">
         <v>1359.895375062967</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.51</v>
+        <v>-4.1</v>
       </c>
       <c r="L41" t="n">
-        <v>3.37</v>
+        <v>4.63</v>
       </c>
       <c r="M41" t="n">
         <v>2.1</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.7</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45839.55208333334</v>
+        <v>45840.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1494.8</v>
+        <v>1491.2</v>
       </c>
       <c r="I42" t="n">
         <v>1493.520106030408</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K42" t="n">
-        <v>9.359999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="L42" t="n">
         <v>2.15</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>4.53</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45888.38541666666</v>
+        <v>45888.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1353</v>
+        <v>1366.5</v>
       </c>
       <c r="I43" t="n">
         <v>1355.975547242439</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>9.27</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L43" t="n">
         <v>2.06</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.82</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1435.8</v>
+        <v>1408</v>
       </c>
       <c r="I44" t="n">
         <v>1412.418398324261</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K44" t="n">
-        <v>5.07</v>
+        <v>3.04</v>
       </c>
       <c r="L44" t="n">
         <v>1.29</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>4.75</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45939.55208333334</v>
+        <v>45940.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1399.7</v>
+        <v>1431</v>
       </c>
       <c r="I45" t="n">
         <v>1423.96219471778</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K45" t="n">
-        <v>0.59</v>
+        <v>-1.63</v>
       </c>
       <c r="L45" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="M45" t="n">
         <v>1.05</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.03</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45975.55208333334</v>
+        <v>45978.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1509.9</v>
+        <v>1471</v>
       </c>
       <c r="I46" t="n">
         <v>1507.489318915764</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K46" t="n">
-        <v>5.51</v>
+        <v>2.8</v>
       </c>
       <c r="L46" t="n">
         <v>2.79</v>
@@ -3063,7 +3614,7 @@
         <v>0.76</v>
       </c>
       <c r="N46" t="n">
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="O46" t="n">
         <v>1.67</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.52</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46006.55208333334</v>
+        <v>46007.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1430.2</v>
+        <v>1466.1</v>
       </c>
       <c r="I47" t="n">
         <v>1461.271000397288</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K47" t="n">
-        <v>2.77</v>
+        <v>0.33</v>
       </c>
       <c r="L47" t="n">
         <v>2.98</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.01</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46015.38541666666</v>
+        <v>46015.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1400.7</v>
+        <v>1396.9</v>
       </c>
       <c r="I48" t="n">
         <v>1400.29886290257</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.46</v>
+        <v>-4.72</v>
       </c>
       <c r="L48" t="n">
-        <v>4.78</v>
+        <v>5.04</v>
       </c>
       <c r="M48" t="n">
         <v>0.71</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>3.94</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46022.55208333334</v>
+        <v>46023.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1391.5</v>
+        <v>1419.7</v>
       </c>
       <c r="I49" t="n">
         <v>1412.168376278731</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>0.39</v>
+        <v>-1.63</v>
       </c>
       <c r="L49" t="n">
-        <v>0.34</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="N49" t="n">
-        <v>2.39</v>
+        <v>3.13</v>
       </c>
       <c r="O49" t="n">
         <v>-1.35</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>4.96</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1442</v>
+        <v>1431.5</v>
       </c>
       <c r="I50" t="n">
         <v>1433.362997975624</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K50" t="n">
-        <v>1.57</v>
+        <v>0.83</v>
       </c>
       <c r="L50" t="n">
         <v>1.94</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.7</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1400</v>
+        <v>1444.9</v>
       </c>
       <c r="I51" t="n">
         <v>1442.813159663062</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>2.2</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L51" t="n">
         <v>4.67</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.18</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1677.6</v>
+        <v>1602</v>
       </c>
       <c r="I52" t="n">
         <v>1607.54033235309</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K52" t="n">
-        <v>16.1</v>
+        <v>10.87</v>
       </c>
       <c r="L52" t="n">
         <v>3.32</v>
@@ -3405,7 +4028,7 @@
         <v>4.94</v>
       </c>
       <c r="N52" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="O52" t="n">
         <v>3.97</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>9.34</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46091.55208333334</v>
+        <v>46092.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1665</v>
+        <v>1710</v>
       </c>
       <c r="I53" t="n">
         <v>1707.96631832921</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.93</v>
+        <v>-6.74</v>
       </c>
       <c r="L53" t="n">
-        <v>4.68</v>
+        <v>7.12</v>
       </c>
       <c r="M53" t="n">
         <v>1.03</v>
       </c>
       <c r="N53" t="n">
-        <v>3.49</v>
+        <v>4.44</v>
       </c>
       <c r="O53" t="n">
         <v>-4.1</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>7.29</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46094.38541666666</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1622.2</v>
+        <v>1610</v>
       </c>
       <c r="I54" t="n">
         <v>1613.539988544205</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.13</v>
+        <v>-5.85</v>
       </c>
       <c r="L54" t="n">
-        <v>5.21</v>
+        <v>6.03</v>
       </c>
       <c r="M54" t="n">
         <v>1.15</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.81</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46167.38541666666</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1544.5</v>
+        <v>1552</v>
       </c>
       <c r="I55" t="n">
         <v>1551.118787967946</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>72.83333333333333</v>
+        <v>73</v>
       </c>
       <c r="K55" t="n">
-        <v>4.07</v>
+        <v>3.6</v>
       </c>
       <c r="L55" t="n">
         <v>4.32</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.29</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1527.8</v>
+        <v>1505</v>
       </c>
       <c r="I56" t="n">
         <v>1506.219447423241</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.56</v>
+        <v>-3.03</v>
       </c>
       <c r="L56" t="n">
         <v>3.96</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.9</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46220.55208333334</v>
+        <v>46223.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1376.6</v>
+        <v>1394.9</v>
       </c>
       <c r="I57" t="n">
         <v>1391.20988856703</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>39</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>8.529999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="L57" t="n">
         <v>5.2</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.52</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1506.7</v>
+        <v>1488.7</v>
       </c>
       <c r="I58" t="n">
         <v>1502.642309952798</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K58" t="n">
-        <v>8.01</v>
+        <v>6.72</v>
       </c>
       <c r="L58" t="n">
         <v>1.94</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.38</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46301.38541666666</v>
+        <v>46301.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>1388.4</v>
+        <v>1400.1</v>
       </c>
       <c r="I59" t="n">
         <v>1395.504069449764</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K59" t="n">
-        <v>6.74</v>
+        <v>5.95</v>
       </c>
       <c r="L59" t="n">
         <v>1.86</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>5.2</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46316.55208333334</v>
+        <v>46317.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1394</v>
+        <v>1374.6</v>
       </c>
       <c r="I60" t="n">
         <v>1388.038133260852</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.44</v>
+        <v>-1.82</v>
       </c>
       <c r="L60" t="n">
-        <v>1.3</v>
+        <v>3.05</v>
       </c>
       <c r="M60" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="N60" t="n">
         <v>2.18</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3921,6 +4652,12 @@
       <c r="Q61" t="n">
         <v>8</v>
       </c>
+      <c r="R61" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6023,7 +6760,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.5</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="6">
@@ -6033,7 +6770,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -6043,7 +6780,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>92.2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -6053,7 +6790,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6063,7 +6800,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43.2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -6073,7 +6810,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.9</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="11">
@@ -6113,7 +6850,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6123,7 +6860,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.13</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="16">
@@ -6133,7 +6870,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.09</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="17">
@@ -6143,7 +6880,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.59</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="18">
@@ -6153,7 +6890,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>64.40000000000001</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="19">
@@ -6163,7 +6900,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.21</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="20">
@@ -6173,7 +6910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="21">
@@ -6183,7 +6920,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.15</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="22">
@@ -6193,7 +6930,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -6203,7 +6940,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6213,7 +6950,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="25">
@@ -6223,7 +6960,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.44</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="26">
@@ -6233,7 +6970,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.08</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="27">
@@ -6243,7 +6980,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.2</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="28">
@@ -6253,7 +6990,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
